--- a/astro-site/public/dl/kit-tareas-sushi-bar/03-seguridad-anisakis-appcc.xlsx
+++ b/astro-site/public/dl/kit-tareas-sushi-bar/03-seguridad-anisakis-appcc.xlsx
@@ -560,7 +560,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>▸ El pescado debe congelarse a -20°C durante minimo 7 dias o -35°C durante 15 horas</t>
+          <t>▸ El pescado debe congelarse a −20 °C en la totalidad del producto durante al menos 24 h, o a −35 °C durante al menos 15 h</t>
         </is>
       </c>
     </row>
@@ -680,10 +680,10 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="34" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Normativa: RD 1420/2006 y Reglamento CE 853/2004 — Obligatorio para todo establecimiento que sirva pescado crudo o poco cocinado</t>
+          <t>Normativa: RD 1021/2022, art. 8.1 (que derogó el RD 1420/2006) y Rgto. (CE) 853/2004, Anexo III, Secc. VIII, Cap. III.D, en la redacción del Rgto. (UE) 1276/2011 — obligatorio en todo establecimiento que sirva pescado crudo o poco cocinado</t>
         </is>
       </c>
     </row>
@@ -1003,10 +1003,10 @@
       <c r="I25" s="9" t="n"/>
     </row>
     <row r="26"/>
-    <row r="27">
+    <row r="27" ht="48" customHeight="1">
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>IMPORTANTE: Si la temperatura sube por encima de -18°C durante la congelacion, reiniciar el conteo de 7 dias</t>
+          <t>IMPORTANTE: el límite crítico es −20 °C. Si la temperatura sube por encima de −20 °C en cualquier momento del tratamiento, este no es válido: reinicia el cómputo completo (24 h, o 15 h si congelas a −35 °C). El −18 °C es el límite del congelador general y no sirve para el tratamiento antiparasitario.</t>
         </is>
       </c>
     </row>
